--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_la_araucania_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_la_araucania_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:14</t>
+    <t xml:space="preserve">2026-09-29 14:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_la_araucania_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_la_araucania_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:12</t>
+    <t xml:space="preserve">2026-09-29 18:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,7 +490,7 @@
         <v>41.28</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>36.57</v>
+        <v>36.56</v>
       </c>
     </row>
     <row r="3">

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_la_araucania_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_la_araucania_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:41</t>
+    <t xml:space="preserve">2026-10-05 04:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -487,10 +487,10 @@
         <v>4.72</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>41.28</v>
+        <v>41.29</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>36.56</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="3">
@@ -501,10 +501,10 @@
         <v>-5.52</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>44.27</v>
+        <v>44.28</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>49.79</v>
+        <v>49.8</v>
       </c>
     </row>
   </sheetData>
